--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/1315-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/1315-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2D670B88-8035-4AEB-836E-41E6BA540707}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04A33EF7-C966-46E7-A921-6D11DC0873D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{36333CA7-314F-467B-B54E-B535777B6316}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{38A224AE-B29E-4171-B1BE-D4C666A3B11A}"/>
   </bookViews>
   <sheets>
     <sheet name="1315-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1490,23 +1490,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62B558AE-2EC1-4AF1-B955-AEFDD35B138C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BC46C00-E1B1-4112-80E1-A522EF836A04}">
   <dimension ref="A1:R55"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="9.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="11.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1534,7 +1534,7 @@
       <c r="Q1" s="30"/>
       <c r="R1" s="22"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1564,7 +1564,7 @@
       <c r="Q2" s="32"/>
       <c r="R2" s="33"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1660,7 +1660,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="37">
         <v>2025</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>6.81</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="39">
         <v>2024</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>6.85</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="37">
         <v>2023</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>8.17</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>3.43</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2158,7 +2158,7 @@
         <v>4.74</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="39">
         <v>2022</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2324,7 +2324,7 @@
         <v>3.08</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="37">
         <v>2021</v>
       </c>
@@ -2378,7 +2378,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2434,7 +2434,7 @@
         <v>3.05</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2490,7 +2490,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="39">
         <v>2020</v>
       </c>
@@ -2544,7 +2544,7 @@
         <v>11.3</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2600,7 +2600,7 @@
         <v>5.19</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="37">
         <v>2019</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>3.81</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="39">
         <v>2018</v>
       </c>
@@ -2764,7 +2764,7 @@
         <v>4.04</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="37">
         <v>2017</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>4.2</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="39">
         <v>2016</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>4.3</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="37">
         <v>2015</v>
       </c>
@@ -2926,7 +2926,7 @@
         <v>4.46</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="39">
         <v>2014</v>
       </c>
@@ -2980,7 +2980,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="37">
         <v>2013</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>3.44</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="39">
         <v>2012</v>
       </c>
@@ -3088,7 +3088,7 @@
         <v>5.89</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="37">
         <v>2011</v>
       </c>
@@ -3142,7 +3142,7 @@
         <v>3.77</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="39">
         <v>2010</v>
       </c>
@@ -3196,7 +3196,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="37">
         <v>2009</v>
       </c>
@@ -3250,7 +3250,7 @@
         <v>4.41</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="39">
         <v>2008</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>5.8</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="37">
         <v>2007</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>3.89</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="39">
         <v>2006</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>6.04</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>2005</v>
       </c>
@@ -3466,7 +3466,7 @@
         <v>6.87</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="39">
         <v>2004</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="37">
         <v>2003</v>
       </c>
@@ -3574,7 +3574,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="39">
         <v>2002</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>9.17</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="37">
         <v>2001</v>
       </c>
@@ -3682,7 +3682,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="39">
         <v>2000</v>
       </c>
@@ -3736,7 +3736,7 @@
         <v>8.6199999999999992</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="37">
         <v>1999</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>5.87</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="39">
         <v>1998</v>
       </c>
@@ -3844,7 +3844,7 @@
         <v>3.58</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="37">
         <v>1997</v>
       </c>
@@ -3898,7 +3898,7 @@
         <v>2.96</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="39">
         <v>1996</v>
       </c>
@@ -3952,7 +3952,7 @@
         <v>5.58</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="37">
         <v>1995</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>5.1100000000000003</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="39">
         <v>1994</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>1993</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>3.33</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="39">
         <v>1992</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>2.04</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="37">
         <v>1991</v>
       </c>
@@ -4222,7 +4222,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="39">
         <v>1990</v>
       </c>
@@ -4276,7 +4276,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="37">
         <v>1989</v>
       </c>
@@ -4330,7 +4330,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="39">
         <v>1987</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="37" t="s">
         <v>49</v>
       </c>
